--- a/Moil Primary School Assets.xlsx
+++ b/Moil Primary School Assets.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="406" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBB4925D-DA96-4240-963A-18D051288596}"/>
+  <xr:revisionPtr revIDLastSave="478" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAF0145B-90E2-4A0B-B186-CF359C9C2942}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monitors" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,8 @@
     <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
     <sheet name="New PC Lab" sheetId="5" r:id="rId5"/>
     <sheet name="Staff Laptop" sheetId="3" r:id="rId6"/>
+    <sheet name="Student Device" sheetId="7" r:id="rId7"/>
+    <sheet name="Ipads" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="501">
   <si>
     <t>Serial Number</t>
   </si>
@@ -887,13 +889,667 @@
   </si>
   <si>
     <t>19.09.2024 - Working Well</t>
+  </si>
+  <si>
+    <t>FL12173</t>
+  </si>
+  <si>
+    <t>Lenevo</t>
+  </si>
+  <si>
+    <t>Lenevo P16S</t>
+  </si>
+  <si>
+    <t>March 23-2026</t>
+  </si>
+  <si>
+    <t>Amrit Lamichhane 01/04/2026</t>
+  </si>
+  <si>
+    <t>Note 2023</t>
+  </si>
+  <si>
+    <t>Warrenty Ends</t>
+  </si>
+  <si>
+    <t>HQHK7S2</t>
+  </si>
+  <si>
+    <t>NTS61847</t>
+  </si>
+  <si>
+    <t>Dell Latitude 3190</t>
+  </si>
+  <si>
+    <t>16.09.2024 - Working Well</t>
+  </si>
+  <si>
+    <t>Desert Rose</t>
+  </si>
+  <si>
+    <t>1JLK7S2</t>
+  </si>
+  <si>
+    <t>NTS61846</t>
+  </si>
+  <si>
+    <t>16.09.2024 -Working well</t>
+  </si>
+  <si>
+    <t>Student Support</t>
+  </si>
+  <si>
+    <t>19XR7S2</t>
+  </si>
+  <si>
+    <t>NTS61844</t>
+  </si>
+  <si>
+    <t>16.09.2024 - can't join domain</t>
+  </si>
+  <si>
+    <t>1FLK7S2</t>
+  </si>
+  <si>
+    <t>NTS61841</t>
+  </si>
+  <si>
+    <t>4QHK7S2</t>
+  </si>
+  <si>
+    <t>NTS61848</t>
+  </si>
+  <si>
+    <t>HFLK7S2</t>
+  </si>
+  <si>
+    <t>NTS61840</t>
+  </si>
+  <si>
+    <t>HDLK7S2</t>
+  </si>
+  <si>
+    <t>NTS61842</t>
+  </si>
+  <si>
+    <t>7KLK7S2</t>
+  </si>
+  <si>
+    <t>NTS61845</t>
+  </si>
+  <si>
+    <t>66VRM13</t>
+  </si>
+  <si>
+    <t>NTS68522</t>
+  </si>
+  <si>
+    <t>8NHK7S2</t>
+  </si>
+  <si>
+    <t>NTS61843</t>
+  </si>
+  <si>
+    <t>90VRM13</t>
+  </si>
+  <si>
+    <t>NTS68519</t>
+  </si>
+  <si>
+    <t>HCWRM13</t>
+  </si>
+  <si>
+    <t>NTS68511</t>
+  </si>
+  <si>
+    <t>16.09.2024 -  Working Well</t>
+  </si>
+  <si>
+    <t>77STST3</t>
+  </si>
+  <si>
+    <t>NTS79418</t>
+  </si>
+  <si>
+    <t>Dell Latitude 11 3120</t>
+  </si>
+  <si>
+    <t>Trolly 3 (Orange)</t>
+  </si>
+  <si>
+    <t>1MYTST3</t>
+  </si>
+  <si>
+    <t>NTS79422</t>
+  </si>
+  <si>
+    <t>C0DYTT3</t>
+  </si>
+  <si>
+    <t>NTS79403</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>7KYTST3</t>
+  </si>
+  <si>
+    <t>NTS79415</t>
+  </si>
+  <si>
+    <t>Trolly 3 Orange)</t>
+  </si>
+  <si>
+    <t>HJYTST3</t>
+  </si>
+  <si>
+    <t>NTS79426</t>
+  </si>
+  <si>
+    <t>Trolly 3 (orange)</t>
+  </si>
+  <si>
+    <t>HGYTST3</t>
+  </si>
+  <si>
+    <t>NTS79424</t>
+  </si>
+  <si>
+    <t>88STST3</t>
+  </si>
+  <si>
+    <t>NTS79416</t>
+  </si>
+  <si>
+    <t>3ZYRST3</t>
+  </si>
+  <si>
+    <t>NTS79409</t>
+  </si>
+  <si>
+    <t>28STST3</t>
+  </si>
+  <si>
+    <t>NTS79427</t>
+  </si>
+  <si>
+    <t>27VRM13</t>
+  </si>
+  <si>
+    <t>NTS68512</t>
+  </si>
+  <si>
+    <t>HDWRM13</t>
+  </si>
+  <si>
+    <t>NTS68524</t>
+  </si>
+  <si>
+    <t>1LWRM13</t>
+  </si>
+  <si>
+    <t>NTS68506</t>
+  </si>
+  <si>
+    <t>6DKYTT3</t>
+  </si>
+  <si>
+    <t>NTS79410</t>
+  </si>
+  <si>
+    <t>914VST3</t>
+  </si>
+  <si>
+    <t>NTS79413</t>
+  </si>
+  <si>
+    <t>11.19.2024 - Working Well</t>
+  </si>
+  <si>
+    <t>FXZRM13</t>
+  </si>
+  <si>
+    <t>NTS68501</t>
+  </si>
+  <si>
+    <t>Trolly 1 (white)</t>
+  </si>
+  <si>
+    <t>3SSRM13</t>
+  </si>
+  <si>
+    <t>NTS68523</t>
+  </si>
+  <si>
+    <t>23.09.2024 - Working Well</t>
+  </si>
+  <si>
+    <t>Trolly 4 (white)</t>
+  </si>
+  <si>
+    <t>6ZYRM13</t>
+  </si>
+  <si>
+    <t>NTS68503</t>
+  </si>
+  <si>
+    <t>9YZRM13</t>
+  </si>
+  <si>
+    <t>NTS68500</t>
+  </si>
+  <si>
+    <t>D1ZRM13</t>
+  </si>
+  <si>
+    <t>NTS68502</t>
+  </si>
+  <si>
+    <t>C2VRM13</t>
+  </si>
+  <si>
+    <t>NTS68516</t>
+  </si>
+  <si>
+    <t>7L1SM13</t>
+  </si>
+  <si>
+    <t>NTS68521</t>
+  </si>
+  <si>
+    <t>G0STST3</t>
+  </si>
+  <si>
+    <t>NTS79401</t>
+  </si>
+  <si>
+    <t>JGWRM13</t>
+  </si>
+  <si>
+    <t>NTS68509</t>
+  </si>
+  <si>
+    <t>DZ2SM13</t>
+  </si>
+  <si>
+    <t>NTS68518</t>
+  </si>
+  <si>
+    <t>36VRM13</t>
+  </si>
+  <si>
+    <t>NTS68513</t>
+  </si>
+  <si>
+    <t>9DWRM13</t>
+  </si>
+  <si>
+    <t>NTS68510</t>
+  </si>
+  <si>
+    <t>7JWRM13</t>
+  </si>
+  <si>
+    <t>NTS68508</t>
+  </si>
+  <si>
+    <t>DLWRM13</t>
+  </si>
+  <si>
+    <t>NTS68505</t>
+  </si>
+  <si>
+    <t>25VRM13</t>
+  </si>
+  <si>
+    <t>NTS68525</t>
+  </si>
+  <si>
+    <t>3WPNM13</t>
+  </si>
+  <si>
+    <t>NTS68517</t>
+  </si>
+  <si>
+    <t>DM1SM13</t>
+  </si>
+  <si>
+    <t>NTS68526</t>
+  </si>
+  <si>
+    <t>5KWRM13</t>
+  </si>
+  <si>
+    <t>NTS68507</t>
+  </si>
+  <si>
+    <t>3CKYTT3</t>
+  </si>
+  <si>
+    <t>NTS79407</t>
+  </si>
+  <si>
+    <t>Trolly 2 (grey)</t>
+  </si>
+  <si>
+    <t>4JYTST3</t>
+  </si>
+  <si>
+    <t>NTS79421</t>
+  </si>
+  <si>
+    <t>JCKYTT3</t>
+  </si>
+  <si>
+    <t>NTS79399</t>
+  </si>
+  <si>
+    <t>48STST3</t>
+  </si>
+  <si>
+    <t>NTS79425</t>
+  </si>
+  <si>
+    <t>89KYTT3</t>
+  </si>
+  <si>
+    <t>NTS79406</t>
+  </si>
+  <si>
+    <t>86STST3</t>
+  </si>
+  <si>
+    <t>NTS79417</t>
+  </si>
+  <si>
+    <t>DCKYTT3</t>
+  </si>
+  <si>
+    <t>NTS79400</t>
+  </si>
+  <si>
+    <t>FKYTST3</t>
+  </si>
+  <si>
+    <t>NTS79419</t>
+  </si>
+  <si>
+    <t>G4STST3</t>
+  </si>
+  <si>
+    <t>NTS79412</t>
+  </si>
+  <si>
+    <t>5RYTST3</t>
+  </si>
+  <si>
+    <t>NTS79414</t>
+  </si>
+  <si>
+    <t>FLYTST3</t>
+  </si>
+  <si>
+    <t>NTS79423</t>
+  </si>
+  <si>
+    <t>21DYTT3</t>
+  </si>
+  <si>
+    <t>NTS79405</t>
+  </si>
+  <si>
+    <t>98KYTT3</t>
+  </si>
+  <si>
+    <t>NTS79404</t>
+  </si>
+  <si>
+    <t>HMYTST3</t>
+  </si>
+  <si>
+    <t>NTS79420</t>
+  </si>
+  <si>
+    <t>Trolly 2 (gray)</t>
+  </si>
+  <si>
+    <t>H1STST3</t>
+  </si>
+  <si>
+    <t>NTS79398</t>
+  </si>
+  <si>
+    <t>FHKYTT3</t>
+  </si>
+  <si>
+    <t>NTS79402</t>
+  </si>
+  <si>
+    <t>7HKYTT3</t>
+  </si>
+  <si>
+    <t>NTS79411</t>
+  </si>
+  <si>
+    <t>23.09.2043 - Working Well</t>
+  </si>
+  <si>
+    <t>B4N9Y74</t>
+  </si>
+  <si>
+    <t>NTS86820</t>
+  </si>
+  <si>
+    <t>Dell Latitude 3140</t>
+  </si>
+  <si>
+    <t>13.02.2025 -Working well</t>
+  </si>
+  <si>
+    <t>25/01/2028</t>
+  </si>
+  <si>
+    <t>Trolly 1(Green)</t>
+  </si>
+  <si>
+    <t>C46MY74</t>
+  </si>
+  <si>
+    <t>NTS86822</t>
+  </si>
+  <si>
+    <t>DQFBY74</t>
+  </si>
+  <si>
+    <t>NTS86813</t>
+  </si>
+  <si>
+    <t>HJW9Y74</t>
+  </si>
+  <si>
+    <t>NTS86816</t>
+  </si>
+  <si>
+    <t>HPQBY74</t>
+  </si>
+  <si>
+    <t>NT586819</t>
+  </si>
+  <si>
+    <t>8YVBY74</t>
+  </si>
+  <si>
+    <t>NTS86809</t>
+  </si>
+  <si>
+    <t>8SV8Y74</t>
+  </si>
+  <si>
+    <t>NTS86810</t>
+  </si>
+  <si>
+    <t>6TV8Y74</t>
+  </si>
+  <si>
+    <t>NTS86811</t>
+  </si>
+  <si>
+    <t>FWH9Y74</t>
+  </si>
+  <si>
+    <t>NTS86823</t>
+  </si>
+  <si>
+    <t>HD5BY74</t>
+  </si>
+  <si>
+    <t>NTS86814</t>
+  </si>
+  <si>
+    <t>5B0BY74</t>
+  </si>
+  <si>
+    <t>3TFBY74</t>
+  </si>
+  <si>
+    <t>NTS86812</t>
+  </si>
+  <si>
+    <t>70R9Y74</t>
+  </si>
+  <si>
+    <t>NTS86817</t>
+  </si>
+  <si>
+    <t>9DNCY74</t>
+  </si>
+  <si>
+    <t>NTS86818</t>
+  </si>
+  <si>
+    <t>13.02.2025 -working well</t>
+  </si>
+  <si>
+    <t>BZTW094</t>
+  </si>
+  <si>
+    <t>NTS87181</t>
+  </si>
+  <si>
+    <t>24.03.2025-working well</t>
+  </si>
+  <si>
+    <t>DMPY4XYJMVT</t>
+  </si>
+  <si>
+    <t>iPad gen 6th</t>
+  </si>
+  <si>
+    <t>working well</t>
+  </si>
+  <si>
+    <t>DMQY42J4JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WNRJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WNGJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4YW7JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4U6VJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4XPJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4U6JJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WYLJMVT</t>
+  </si>
+  <si>
+    <t>DMQY41EFJMVT</t>
+  </si>
+  <si>
+    <t>DMPCMACVMF3Q</t>
+  </si>
+  <si>
+    <t>DMPY4W5GJMVT</t>
+  </si>
+  <si>
+    <t>DMQY43AGJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4VULJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4TBJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4ZM8JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WT6JMVT</t>
+  </si>
+  <si>
+    <t>DMQY41M5JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4YPJJMVT</t>
+  </si>
+  <si>
+    <t>DMQY42S7JMVT</t>
+  </si>
+  <si>
+    <t>DMQY42JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WM0JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WLAJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WQWJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WRJ9MVT</t>
+  </si>
+  <si>
+    <t>DMQY410BJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WV0JMVT</t>
+  </si>
+  <si>
+    <t>DMQY42L0JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4WG9JMVT</t>
+  </si>
+  <si>
+    <t>DMPY4L6ZJMVT</t>
+  </si>
+  <si>
+    <t>DMQY40BHJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4X1FJMVT</t>
+  </si>
+  <si>
+    <t>DMPY4W9VJMVT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -958,8 +1614,15 @@
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -982,6 +1645,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1225,7 +1900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1328,6 +2003,11 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3265,14 +3945,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8542B7-A421-458E-81C3-109475F5811D}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
     <col min="4" max="4" width="29.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="6" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" style="6" customWidth="1"/>
     <col min="7" max="7" width="30.85546875" style="6" customWidth="1"/>
     <col min="8" max="8" width="39.7109375" style="6" customWidth="1"/>
@@ -3982,6 +4662,2368 @@
         <v>282</v>
       </c>
     </row>
+    <row r="30" spans="1:8">
+      <c r="B30" t="s">
+        <v>283</v>
+      </c>
+      <c r="C30" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" t="s">
+        <v>285</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA28D04A-9773-4936-AF9D-2B9EB789D364}">
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="33.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D13" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D14" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F14" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D15" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D16" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D17" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F17" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D18" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F18" s="42">
+        <v>45981</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D19" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F19" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D20" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F20" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D21" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F21" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D22" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F22" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D23" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F23" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D24" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F24" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D25" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F25" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D26" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F26" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D27" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="F27" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F28" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D29" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F29" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D30" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F30" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D31" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F31" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F32" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="F33" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D34" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F34" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D35" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F35" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D36" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F36" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D37" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F37" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D38" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F38" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D39" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F39" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D40" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F40" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D41" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F41" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D42" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F42" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D43" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F43" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D44" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F44" s="42">
+        <v>45006</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D45" s="16">
+        <v>46101</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F45" s="42">
+        <v>45005</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D46" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F46" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D47" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F47" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D48" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F48" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D49" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F49" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D50" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F50" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D51" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F51" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D52" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F52" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D53" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F53" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D54" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F54" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D55" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F55" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D56" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F56" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D57" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F57" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D58" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F58" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D59" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F59" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D60" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="F60" s="42">
+        <v>45980</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D61" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F61" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D62" s="16">
+        <v>46348</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="F62" s="42">
+        <v>45979</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D63" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D64" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D65" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D66" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D67" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D68" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D69" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D70" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D71" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D72" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D73" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D74" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D75" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D76" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D77" s="16">
+        <v>46047</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="F77" s="42">
+        <v>47060</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D78" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E78" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F78" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G78" s="40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D79" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F79" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G79" s="40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D80" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F80" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G80" s="40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D81" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F81" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G81" s="40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD9CC85-01A7-433D-B719-8AAB560F16A2}">
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="4" width="26.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="44" t="s">
+        <v>469</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="44" t="s">
+        <v>470</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="44" t="s">
+        <v>471</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="44" t="s">
+        <v>473</v>
+      </c>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="44" t="s">
+        <v>474</v>
+      </c>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="44" t="s">
+        <v>475</v>
+      </c>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="44" t="s">
+        <v>476</v>
+      </c>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="44" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="44" t="s">
+        <v>479</v>
+      </c>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="44" t="s">
+        <v>480</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="44" t="s">
+        <v>482</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="44" t="s">
+        <v>483</v>
+      </c>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="44" t="s">
+        <v>484</v>
+      </c>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="44" t="s">
+        <v>489</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="44" t="s">
+        <v>490</v>
+      </c>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="44" t="s">
+        <v>491</v>
+      </c>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="44" t="s">
+        <v>492</v>
+      </c>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="44" t="s">
+        <v>493</v>
+      </c>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="44" t="s">
+        <v>494</v>
+      </c>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="44" t="s">
+        <v>495</v>
+      </c>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="44" t="s">
+        <v>496</v>
+      </c>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="44" t="s">
+        <v>497</v>
+      </c>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="44" t="s">
+        <v>498</v>
+      </c>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="44" t="s">
+        <v>499</v>
+      </c>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="44" t="s">
+        <v>500</v>
+      </c>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44" t="s">
+        <v>468</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
